--- a/www/download/IND.gdp.s.du.rpPE.xlsx
+++ b/www/download/IND.gdp.s.du.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82258.5369991162</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82927.9646355144</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83426.3094777427</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85645.4242224099</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90879.4537667787</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94968.9396737349</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92806.9749183511</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97030.1128115241</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106017.883447389</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115990.685307166</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127259.137666632</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135875.499861785</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154733.81311373</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180404.869941726</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176018.507149945</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43089.3895557271</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43164.2451708578</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43176.1862887907</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43537.9933650686</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45840.7632056615</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46814.1274498288</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46090.7212011987</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46821.7534827923</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48440.4482865585</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56011.0069365192</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58148.7441805365</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59781.9311293388</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66341.0122156756</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73170.7893342199</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64731.9751885077</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29530.2677962984</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29483.47376986</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29460.6662230263</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29792.5672473833</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31198.3165499022</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32601.7092704141</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31896.0087001403</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31961.0544997501</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33689.1283189779</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37589.189274344</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40070.4016354868</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42139.7670337925</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47592.7380314504</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54335.0723977233</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49589.1991151797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27922.5566771413</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28351.2793358841</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26333.3197196747</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23438.3804043396</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23156.4166637982</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21702.7756185011</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20172.5949286297</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20228.0089195266</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23076.9738471463</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26520.5233720357</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28973.3327154419</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31289.3814442755</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36488.5560935144</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40644.9882590703</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37461.4030524272</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588698.694895651</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>583806.848008126</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>595326.218207053</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590049.320044176</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>641295.468530552</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>671085.384739413</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659815.956931614</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>695213.313942798</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>772776.287233765</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>894003.732920413</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988586.834491407</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1077263.8220145</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1278942.44868169</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1476147.07904571</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1384092.44147875</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162899.508478658</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>163778.710092696</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164536.578005241</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166211.439951723</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174111.924297248</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181166.032270564</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172898.30706054</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175503.417162214</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186393.573559595</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209185.131925863</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>224605.15605166</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236753.812811056</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266276.196111983</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288795.116632083</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261530.85480464</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.137</t>
+          <t>5136958.09150044</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.254</t>
+          <t>5254499.18601592</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.245</t>
+          <t>5244730.26151501</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5.132</t>
+          <t>5131958.54565139</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.369</t>
+          <t>5368859.88898917</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5.428</t>
+          <t>5427560.90992299</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.361</t>
+          <t>5360864.37667214</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.583</t>
+          <t>5582522.42994156</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6.283</t>
+          <t>6283055.88107205</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6.926</t>
+          <t>6926071.34768661</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7.654</t>
+          <t>7653763.13717111</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.522</t>
+          <t>8521720.60554819</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9.909</t>
+          <t>9908698.23841198</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11.481</t>
+          <t>11480535.7887928</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10.725</t>
+          <t>10725216.2012985</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3437.99281708527</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3407.9247792947</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3265.63122710536</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3157.12034458516</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3264.21323419882</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3400.01829535563</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3376.11212077335</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3458.45012472932</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3755.90425099119</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4051.79029974529</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4345.09506930324</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4611.5859411883</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5506.84260305064</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5950.16445875924</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5506.41200925739</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83700.031511625</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83625.3112048552</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81576.2538703629</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79746.2194361063</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79849.5838120782</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79911.3715536038</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74314.3875944004</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74101.4111111053</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76326.4248832618</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84782.8618301416</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92023.6680688226</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96928.4460754794</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108457.35954581</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120518.800158657</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106993.739435842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>460955.746593435</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>440738.610941901</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>426079.45405208</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>441903.495798313</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>451164.664570894</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>451366.515823202</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>429442.109326658</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428137.7302464</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>455955.607027131</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>505909.529122195</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>517634.393930969</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>528248.084819796</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>590060.521435862</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>641927.397255835</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589476.264341622</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33220.8883189189</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33100.6992648396</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33692.2332265523</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34878.0564805464</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36832.0643487629</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37738.9546591698</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36700.62879217</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37239.0540332797</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39077.2526887227</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42543.6651325491</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45811.3228242925</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48376.2347646759</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50290.5523624886</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56825.6250902014</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51436.6533996124</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127046.160667281</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134974.989168819</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139750.814141308</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148675.877330131</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162653.668397969</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177881.439228511</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177573.057767999</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187794.918588855</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205340.092493065</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229904.881303855</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>257577.605635101</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>277438.512356248</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>313356.959383847</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>332956.491382533</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290017.690613198</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13066.7422023193</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12457.4679413207</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11953.0692458048</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11380.8724602485</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10806.6466800723</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10709.1623142862</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10653.5447006493</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10727.1739929267</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11592.6739770901</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13247.7289002815</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14102.0538901902</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15363.7576426562</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17167.8230840404</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18085.4173479849</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14613.2366895119</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33257.3249378839</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33586.841647534</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34329.3143395187</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34824.3626183468</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36893.5421299117</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37413.1810937416</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36452.7652515261</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37086.2874108669</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38547.8030359968</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42871.1052297901</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45730.9365197529</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48112.6646182925</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54241.4279329165</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59147.8475825227</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53648.6325221211</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>230958.265091265</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233255.428203083</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231648.977282782</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234900.836153188</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248313.431496289</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249518.312866072</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243258.650064106</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>242351.942555105</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>253687.293771689</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281185.307375659</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>301556.329997097</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>315020.532153848</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364696.812103465</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403532.051258606</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>368499.723684023</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293111.457299601</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>293670.543842764</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>303030.095619386</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311899.074990278</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329129.311669984</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>338852.57755982</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>327917.593756611</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336941.493118673</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353081.044743598</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384067.40649896</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>410967.472621541</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>429519.865031598</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>476382.471021919</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509344.214455571</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474281.170135221</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41081.7271131664</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41088.1133375487</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39998.1404851688</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42162.1014350872</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44782.6415268011</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45395.2897952104</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43546.4966590536</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44707.6077344939</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47532.9953669116</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55265.1939759254</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57865.5898000996</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64559.8500177109</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72987.0757763248</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78317.0142120947</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73414.3611109199</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67298.5810530403</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66083.9877586799</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64712.6310077447</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65862.9089440313</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71582.5208783358</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70666.6102025676</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66058.398619085</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67319.9326813919</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70812.2851952957</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78126.7385436427</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80675.2649834619</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84561.897725362</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92927.5997794594</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96013.4198589481</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90192.9305513718</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>466999.403915937</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>486778.324235505</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475490.767647769</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>484901.79394316</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>541353.590502682</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579367.100652081</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>561156.994649973</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>594729.430255082</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>671239.404842241</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>742285.969908195</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>708404.75874265</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>706367.504075448</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826110.587329884</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>916503.539993732</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866199.007232921</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.428</t>
+          <t>4427738.02637397</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.622</t>
+          <t>4622292.20393484</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.638</t>
+          <t>4638312.5586997</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.626</t>
+          <t>4625868.70887287</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.757</t>
+          <t>4756987.03288277</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.077</t>
+          <t>5076831.78832807</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.207</t>
+          <t>5207010.09929194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>5330394.98524708</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6170329.97738708</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6.929</t>
+          <t>6929329.37823123</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7.595</t>
+          <t>7594883.47694969</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>7.984</t>
+          <t>7984495.8226159</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>8.827</t>
+          <t>8827054.88993747</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>9.765</t>
+          <t>9764830.98727841</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>9.065</t>
+          <t>9064805.92709822</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18324.0460096191</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19564.0836412369</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19877.4986198393</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21176.9149884187</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23397.4562352951</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24681.7787842365</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24500.9975308024</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25638.6316731988</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28043.1428590535</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31994.3033853972</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35931.3860649177</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39663.7198498962</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45388.9530937309</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51238.1000916391</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45599.7877806489</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>173366.774708823</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177145.639367557</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179088.722529892</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>185710.322245279</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>196581.335727239</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>199195.970538562</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188277.55100878</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192830.994108709</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211282.365289758</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232457.3502677</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255405.653557054</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>273846.581220282</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311620.564021773</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346876.126181983</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>309325.36931892</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920336.348612209</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>921899.231743729</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>910684.985454204</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>888859.514594669</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>907581.088431255</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>924508.670914993</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>887477.338347363</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876946.489822266</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>926815.634230419</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1012828.47266606</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1055493.00040127</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>1096551.58482507</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1211046.76488684</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1261484.683964</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1079944.62190177</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>460720.856254885</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>458679.547851032</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456500.605566401</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442389.69728734</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>471676.596917161</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>504708.282692167</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>491700.241981957</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>510208.74768516</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546488.354394998</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>625014.118269886</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634040.282801775</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>654950.645683528</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>701175.732386541</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>756986.457205295</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699825.985280571</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26998.2743750222</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26659.0536336654</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25351.8010982647</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25871.285125968</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24994.4902629122</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26419.557535931</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24306.3510926547</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24327.1932130763</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26270.2450819817</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28904.8137844264</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32845.1617777098</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33503.3663557763</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39252.383023802</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42828.7727205696</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36554.739102773</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1796.86237828231</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1806.01677720233</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1861.65172885194</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1951.09471115841</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2063.1067757652</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2201.31319815166</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2182.32196440225</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2282.90371643473</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2282.24475940815</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2960.34909333914</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3245.9788157852</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3323.15334036488</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3860.14529109365</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4481.40453380025</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4837.92611064652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14547.7475624443</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14229.7865343349</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13904.1845477367</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13346.1853690675</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12988.654856068</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12235.5465024883</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11445.0404058476</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11283.0789278387</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11961.5360937925</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13386.449577539</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13975.5484615603</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15166.6583166187</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17109.9076350375</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18395.2673138034</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13145.1924788109</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>409032.545282892</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>427973.156769223</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>440205.562760546</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>447934.27368636</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475479.396545884</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491210.043485699</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483219.604623724</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494849.789645386</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>540839.844227556</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>621412.376781245</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>693063.84806544</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>720092.376899088</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808393.850865898</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>944679.362328611</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>857180.170153009</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1081.51294717871</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1076.04346394231</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1020.59954525404</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>981.288096912751</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1029.63491017034</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1050.72048986818</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>885.010743328213</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1050.58164600886</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1121.30660632351</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1318.07254465421</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1366.66051193781</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1437.37306171148</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1594.61006750721</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1735.22894987053</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1652.28386555998</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61598.596811174</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63150.8992262119</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64527.1672694687</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65714.3063120501</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71780.5967400243</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68792.162630838</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68049.7328147961</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71497.3870529513</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78765.566041863</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88491.0336570706</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93519.7739516288</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97437.3715930869</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109055.092650156</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120244.939070605</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111529.870110177</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246325.099247245</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246086.465237184</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>243354.985293098</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241872.690437412</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241877.550572783</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237147.120698705</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208899.636983193</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204531.577906419</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219640.083644123</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246397.729391842</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268858.338815226</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>288285.517909089</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>327185.325579692</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>369348.928173493</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339261.377086269</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31450.4636141377</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31547.4527963762</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30061.3974242016</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28745.1483390372</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30372.0823871641</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31172.902640038</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30462.1764687723</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31013.9674441628</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34180.4386853597</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38501.4001813686</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40992.299259413</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44934.334473766</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51461.6679932652</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57136.27045065</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53209.7565647891</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81087.952765497</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81793.4813981175</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73504.86482758</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67634.3005374344</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79532.53770302</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77791.2725659652</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74929.3782904682</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72653.8312526314</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81514.9723401441</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86470.1711539088</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92420.9066705362</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98407.5272554212</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112854.818184258</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127785.724877608</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119076.974842165</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1441672.09001595</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1386737.93281619</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1300743.72927882</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>1232262.52878835</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1280472.24225113</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1310130.88841617</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1267057.79369714</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1281486.96578965</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>1352004.96082989</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1487442.89152864</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>1573027.94474188</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1629204.04010511</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>1812752.55553181</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>1953712.62315921</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1745199.53432436</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35119.3093276779</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33519.926754042</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32461.7026967423</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31387.9593769421</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31175.994802934</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30768.4554303691</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29443.7868244969</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28253.9347509758</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28932.3094559331</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32807.3466879127</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35170.2684860809</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36048.2165561206</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41003.6923487926</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46273.5779259989</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41462.6403307728</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13693.7813481546</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13104.7437778917</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12650.7984244438</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12467.7890509765</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13121.4429910113</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13662.6595269743</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12536.8440435785</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12844.2303240588</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13884.6231413978</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15418.5680530003</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16462.166313738</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17361.562690533</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19635.1748142384</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22526.0481390571</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20533.4816938669</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53018.991747932</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52658.4600083432</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51607.0706008839</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52355.1341031555</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55941.1787480816</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61159.3406577349</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60261.5140869225</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60943.3273717046</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63503.073321043</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70459.0185949334</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75162.4757451426</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78593.0835960777</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89940.0115063371</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99144.3452167264</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88578.4654578087</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163459.826273482</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174449.909905898</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175612.711475221</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166924.855500791</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171370.834967232</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164608.551954535</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159981.123661029</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165016.941612499</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183573.141116975</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194752.398055098</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222861.111840064</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>230093.969739857</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>255890.091780682</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>289985.739051684</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>263454.870580756</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120015.377634149</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121882.366436044</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126100.094519875</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128354.0300244</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136361.832643548</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143270.915784242</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132607.92529011</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137897.637958225</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149860.741784279</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169003.543047719</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186004.380228723</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>197444.348835825</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226690.082934582</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251773.176296762</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231219.5474907</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1458735.03627857</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1469259.85806542</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1472701.48981956</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.525</t>
+          <t>1525156.55100507</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1590676.5811345</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.647</t>
+          <t>1647355.54926686</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1567293.86793046</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1552406.73628783</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1604282.73487055</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.797</t>
+          <t>1797162.61950956</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1917126.6393196</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.036</t>
+          <t>2036095.6333184</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.264</t>
+          <t>2264397.27233682</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2415198.5581402</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.141</t>
+          <t>2141364.98538409</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12150094.8344446</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12.507</t>
+          <t>12507386.1065086</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12.645</t>
+          <t>12645414.9061343</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12.753</t>
+          <t>12753043.4649562</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13.432</t>
+          <t>13432339.5751519</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>14.325</t>
+          <t>14324756.5200355</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14.478</t>
+          <t>14477665.4638803</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>15.225</t>
+          <t>15225314.3627036</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17.118</t>
+          <t>17118453.7304758</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>19.651</t>
+          <t>19651051.1816472</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>21.432</t>
+          <t>21432482.1093162</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>23.264</t>
+          <t>23263842.9246669</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>26.668</t>
+          <t>26668387.2081404</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30469776.7214131</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>29.044</t>
+          <t>29044193.057349</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.236</t>
+          <t>30235705.7214385</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30.902</t>
+          <t>30901682.3160021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.948</t>
+          <t>30948066.009897</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.925</t>
+          <t>30924934.4342304</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32399769.354889</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.932</t>
+          <t>33931780.4250671</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33.805</t>
+          <t>33805189.4806777</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.028</t>
+          <t>35027549.818753</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>39.074</t>
+          <t>39074429.9846792</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>44.107</t>
+          <t>44107177.3816536</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>47.932</t>
+          <t>47932440.648091</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>51.565</t>
+          <t>51564713.5679737</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>58.677</t>
+          <t>58677009.8300298</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>66.25</t>
+          <t>66249598.7299419</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>61.995</t>
+          <t>61994876.9681192</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
